--- a/task-reviews/physics/task_physics_circuits_equivalent_resistance/task_physics_circuits_equivalent_resistance.xlsx
+++ b/task-reviews/physics/task_physics_circuits_equivalent_resistance/task_physics_circuits_equivalent_resistance.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="total_resistance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="missing_resistor_value" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="total_resistance" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -132,6 +133,1261 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1768,36 +3024,36 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>total_resistance</t>
+          <t>missing_resistor_value</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
+Evidence format: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":2}</t>
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 10}</t>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 4}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1815,12 +3071,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0004.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0002.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0004.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0002.json</t>
         </is>
       </c>
     </row>
@@ -1832,31 +3088,1728 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>474277600027344</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0023.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="172.5" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>709501439747477</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0022.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="172.5" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 7}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1125183293749637</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0001.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="172.5" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1223995386165486</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0005.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="172.5" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 7}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1607066970284824</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0000.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="172.5" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1868376080195241</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0024.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="172.5" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1951869731340821</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0008.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="172.5" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2590099989459345</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0016.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="172.5" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2840125590574695</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0013.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="172.5" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Work from the labeled resistor boxes between terminals A and B. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Work from the labeled resistor boxes between terminals A and B. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>3345619949818639</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0006.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="172.5" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>3786517310065736</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0019.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="172.5" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>3889704498807161</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0003.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="172.5" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Determine the requested equivalent resistance from the diagram. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Determine the requested equivalent resistance from the diagram. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>3901398368165359</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0009.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="172.5" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4117998854336417</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0021.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="172.5" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>4192774504354655</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0010.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="172.5" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>4480068874378025</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0014.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="172.5" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>4616140200899754</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0017.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="172.5" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>5295255370861532</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0004.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="172.5" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>5922211512362343</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0015.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="172.5" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>5937499668052791</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0020.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="172.5" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>6270632950726452</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0012.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="172.5" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>6477486155686751</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0011.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="172.5" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>8300710001772333</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0018.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="172.5" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>8435851177447991</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0007.png</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0007.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>evidence_image</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>task_variant</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>prompt</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>prompt_answer_only</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>answer_evidence</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>answer_type</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>evidence_type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>instance_seed</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>image_path</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>data_path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="172.5" customHeight="1">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"answer":2}</t>
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>173078022734026</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0004.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="172.5" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 2}</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1875,16 +4828,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>173078022734026</v>
+        <v>660400536858167</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0009.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0020.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0009.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0020.json</t>
         </is>
       </c>
     </row>
@@ -1901,118 +4854,118 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>893633062788246</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0013.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="172.5" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[190.0, 257.0, 286.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[190.0, 257.0, 286.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 17}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>1125183293749637</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0002.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="172.5" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K5" t="n">
-        <v>1223995386165486</v>
+        <v>1055229645825624</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0010.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0023.png</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0010.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0023.json</t>
         </is>
       </c>
     </row>
@@ -2034,7 +4987,7 @@
 Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2043,7 +4996,7 @@
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"answer":2}</t>
+{"answer":8}</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2071,12 +5024,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0023.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0011.png</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0023.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0011.json</t>
         </is>
       </c>
     </row>
@@ -2098,7 +5051,7 @@
 Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2107,7 +5060,7 @@
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"answer":2}</t>
+{"answer":8}</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2135,12 +5088,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0022.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0010.png</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0022.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0010.json</t>
         </is>
       </c>
     </row>
@@ -2157,31 +5110,31 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":2}</t>
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 9}</t>
+          <t>{"evidence": [[190.0, 257.0, 286.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 14}</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+          <t>[[190.0, 257.0, 286.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2195,16 +5148,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1607066970284824</v>
+        <v>2068722755382386</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0000.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0021.png</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0000.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0021.json</t>
         </is>
       </c>
     </row>
@@ -2220,795 +5173,795 @@
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 17}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>1951869731340821</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0016.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="172.5" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Work from the labeled resistor boxes between terminals A and B. What integer equivalent resistance does this resistor network have between A and B?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Work from the labeled resistor boxes between terminals A and B. What integer equivalent resistance does this resistor network have between A and B?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2271922067432330</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0024.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="172.5" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 12}</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K9" t="n">
         <v>2299605336486020</v>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0007.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0007.json</t>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0003.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0003.json</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="172.5" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
+    <row r="10" ht="172.5" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Work from the labeled resistor boxes between terminals A and B. What integer equivalent resistance does this resistor network have between A and B?
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Work from the labeled resistor boxes between terminals A and B. What integer equivalent resistance does this resistor network have between A and B?
+Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 14}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>3345619949818639</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0012.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0012.json</t>
+      <c r="K10" t="n">
+        <v>2497391323432836</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0017.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0017.json</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="172.5" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
+    <row r="11" ht="172.5" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 14}</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K11" t="n">
         <v>3380173888818303</v>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0011.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0011.json</t>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0005.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0005.json</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="172.5" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
+    <row r="12" ht="172.5" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 1}</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K12" t="n">
         <v>3826916508657120</v>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0003.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0003.json</t>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0001.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0001.json</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="172.5" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
+    <row r="13" ht="172.5" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 17}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>3889704498807161</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0006.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0006.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="172.5" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>3901398368165359</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0021.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="172.5" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Work from the labeled resistor boxes between terminals A and B. What integer equivalent resistance does this resistor network have between A and B?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Work from the labeled resistor boxes between terminals A and B. What integer equivalent resistance does this resistor network have between A and B?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>4668544630995035</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0017.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="172.5" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What integer equivalent resistance does this resistor network have between A and B?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What integer equivalent resistance does this resistor network have between A and B?
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 12}</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K18" t="n">
+      <c r="K13" t="n">
         <v>4947651378094025</v>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0014.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0014.json</t>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0006.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0006.json</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="172.5" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
+    <row r="14" ht="172.5" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>5027780694797899</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0015.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="172.5" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. What integer equivalent resistance does this resistor network have between A and B?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. What integer equivalent resistance does this resistor network have between A and B?
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="K15" t="n">
         <v>5138198624586159</v>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0019.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0019.json</t>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0009.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0009.json</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="172.5" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
+    <row r="16" ht="172.5" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. What integer equivalent resistance does this resistor network have between A and B?
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Work from the labeled resistor boxes between terminals A and B. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. What integer equivalent resistance does this resistor network have between A and B?
+Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Work from the labeled resistor boxes between terminals A and B. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>5186789823409140</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0016.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="172.5" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 17}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K20" t="n">
-        <v>5295255370861532</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0008.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0008.json</t>
+      <c r="K17" t="n">
+        <v>5944729093912585</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0022.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0022.json</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="172.5" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
+    <row r="18" ht="172.5" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Determine the requested equivalent resistance from the diagram. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Determine the requested equivalent resistance from the diagram. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6148348830281278</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0024.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="172.5" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"answer":2}</t>
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 11}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>7249862871102077</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0008.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="172.5" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 17}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>7513188673007291</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0018.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="172.5" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 11}</t>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3027,16 +5980,16 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>7249862871102077</v>
+        <v>7790233719936158</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0018.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0019.png</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0018.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0019.json</t>
         </is>
       </c>
     </row>
@@ -3052,311 +6005,311 @@
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>7830445062449040</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0012.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="172.5" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What integer equivalent resistance does this resistor network have between A and B?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What integer equivalent resistance does this resistor network have between A and B?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 18}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>7935148462875896</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0014.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="172.5" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Determine the requested equivalent resistance from the diagram. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Determine the requested equivalent resistance from the diagram. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K22" t="n">
+      <c r="K24" t="n">
         <v>7985343017561541</v>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0005.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0005.json</t>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0002.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0002.json</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="172.5" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
+    <row r="25" ht="172.5" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 7}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>8435851177447991</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0013.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0013.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="172.5" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 18}</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K24" t="n">
+      <c r="K25" t="n">
         <v>8514324742857824</v>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0001.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0001.json</t>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0000.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0000.json</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="172.5" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
+    <row r="26" ht="172.5" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 13}</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K25" t="n">
+      <c r="K26" t="n">
         <v>8812400365677262</v>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0015.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="172.5" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. What integer equivalent resistance does this resistor network have between A and B?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[322,167,418,213],[322,257,418,303],[322,347,418,393]],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. What integer equivalent resistance does this resistor network have between A and B?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>8930969253933596</v>
-      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/default/0020.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0007.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/default/0020.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0007.json</t>
         </is>
       </c>
     </row>

--- a/task-reviews/physics/task_physics_circuits_equivalent_resistance/task_physics_circuits_equivalent_resistance.xlsx
+++ b/task-reviews/physics/task_physics_circuits_equivalent_resistance/task_physics_circuits_equivalent_resistance.xlsx
@@ -3029,7 +3029,199 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>278772381202056</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0007.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="172.5" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>418977592921915</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0005.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="172.5" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>712844117119872</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0012.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="172.5" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3037,63 +3229,63 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 7}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>[[176.0, 353.0, 272.0, 399.0]]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>141028188354687</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0002.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0002.json</t>
+      <c r="K5" t="n">
+        <v>945423047749785</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0006.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0006.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="172.5" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="6" ht="172.5" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>missing_resistor_value</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Answer using only the resistor values shown in the network. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3101,63 +3293,63 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Answer using only the resistor values shown in the network. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>474277600027344</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0023.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0023.json</t>
+      <c r="K6" t="n">
+        <v>985168828526994</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0004.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0004.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="172.5" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="7" ht="172.5" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>missing_resistor_value</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3165,63 +3357,447 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
 Return a valid JSON object with key "answer".
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1351017546901334</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0020.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="172.5" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1680700451011549</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0009.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="172.5" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2909727922937639</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0015.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="172.5" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>3584273931974755</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0023.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="172.5" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Determine the requested equivalent resistance from the diagram. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Determine the requested equivalent resistance from the diagram. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>[[176.0, 353.0, 272.0, 399.0]]</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>709501439747477</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0022.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0022.json</t>
+      <c r="K11" t="n">
+        <v>3779473663499662</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0010.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0010.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="172.5" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="12" ht="172.5" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>missing_resistor_value</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>3906255867824926</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0019.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="172.5" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 11}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>4212431905210786</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0008.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="172.5" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3229,63 +3805,63 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 7}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>[[176.0, 353.0, 272.0, 399.0]]</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>1125183293749637</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0001.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0001.json</t>
+      <c r="K14" t="n">
+        <v>4614071103821109</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0017.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0017.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="172.5" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="15" ht="172.5" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>missing_resistor_value</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3293,63 +3869,127 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>5189991571579559</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0002.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="172.5" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Answer using only the resistor values shown in the network. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Answer using only the resistor values shown in the network. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>1223995386165486</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0005.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0005.json</t>
+      <c r="K16" t="n">
+        <v>5192253131022505</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0000.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0000.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="172.5" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="17" ht="172.5" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>missing_resistor_value</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3357,63 +3997,63 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 7}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>[[176.0, 353.0, 272.0, 399.0]]</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>1607066970284824</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0000.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0000.json</t>
+      <c r="K17" t="n">
+        <v>6662188879944179</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0021.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0021.json</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="172.5" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
+    <row r="18" ht="172.5" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>missing_resistor_value</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3421,63 +4061,255 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6717988806220528</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0024.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="172.5" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>6753696303575526</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0016.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="172.5" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>1868376080195241</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0024.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0024.json</t>
+      <c r="K20" t="n">
+        <v>6994361047359585</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0011.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0011.json</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="172.5" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
+    <row r="21" ht="172.5" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>missing_resistor_value</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>7001841890215397</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0013.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="172.5" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3485,63 +4317,191 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>7098362396424255</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0003.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="172.5" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Work from the labeled resistor boxes between terminals A and B. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Work from the labeled resistor boxes between terminals A and B. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 12}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>1951869731340821</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0008.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0008.json</t>
+      <c r="K23" t="n">
+        <v>7433576612134137</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0001.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0001.json</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="172.5" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
+    <row r="24" ht="172.5" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>missing_resistor_value</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>7643448629001720</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0018.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="172.5" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3549,383 +4509,63 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 10}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2590099989459345</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0016.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="172.5" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>[[176.0, 353.0, 272.0, 399.0]]</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>2840125590574695</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0013.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0013.json</t>
+      <c r="K25" t="n">
+        <v>8405728320064799</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0014.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0014.json</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="172.5" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
+    <row r="26" ht="172.5" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>missing_resistor_value</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Work from the labeled resistor boxes between terminals A and B. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Work from the labeled resistor boxes between terminals A and B. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 10}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>3345619949818639</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0006.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0006.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="172.5" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>3786517310065736</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0019.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="172.5" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>3889704498807161</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0003.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="172.5" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Determine the requested equivalent resistance from the diagram. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Determine the requested equivalent resistance from the diagram. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>3901398368165359</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0009.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0009.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="172.5" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3933,686 +4573,46 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>4117998854336417</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0021.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="172.5" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>4192774504354655</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0010.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="172.5" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>4480068874378025</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0014.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="172.5" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>4616140200899754</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0017.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="172.5" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>5295255370861532</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0004.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="172.5" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>5922211512362343</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0015.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="172.5" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 12}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>5937499668052791</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0020.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="172.5" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>6270632950726452</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0012.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0012.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="172.5" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Work from the labeled resistor boxes between terminals A and B. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>6477486155686751</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0011.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="172.5" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8300710001772333</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0018.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0018.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="172.5" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>8435851177447991</v>
+        <v>8414218812010040</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0007.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0022.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0007.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0022.json</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,135 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>39185639326284</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0014.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="172.5" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What integer equivalent resistance does this resistor network have between A and B?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What integer equivalent resistance does this resistor network have between A and B?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[654.0, 257.0, 750.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 7}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[654.0, 257.0, 750.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>205676244115051</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0002.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="172.5" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -4734,127 +4862,63 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>173078022734026</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0004.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0004.json</t>
+      <c r="K4" t="n">
+        <v>437924746508586</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0005.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0005.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="172.5" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="5" ht="172.5" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>660400536858167</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0020.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="172.5" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B with three or four parallel labeled resistor branches. Determine the requested equivalent resistance from the diagram. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -4862,63 +4926,63 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B with three or four parallel labeled resistor branches. Determine the requested equivalent resistance from the diagram. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>893633062788246</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0013.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0013.json</t>
+      <c r="K5" t="n">
+        <v>1272734665395217</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0017.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0017.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="172.5" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="6" ht="172.5" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -4926,63 +4990,127 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 17}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>1055229645825624</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0023.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0023.json</t>
+      <c r="K6" t="n">
+        <v>1474459048523441</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0021.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0021.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="172.5" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="7" ht="172.5" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1926147751723478</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0016.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="172.5" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -4990,63 +5118,127 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 17}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2093720560009143</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0023.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="172.5" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 16}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>1245112531061819</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0011.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0011.json</t>
+      <c r="K9" t="n">
+        <v>3309929876814048</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0022.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0022.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="172.5" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="10" ht="172.5" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. What integer equivalent resistance does this resistor network have between A and B?
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -5054,63 +5246,63 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. What integer equivalent resistance does this resistor network have between A and B?
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[654.0, 257.0, 750.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[654.0, 257.0, 750.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>1533712878430802</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0010.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0010.json</t>
+      <c r="K10" t="n">
+        <v>3591229892990988</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0001.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0001.json</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="172.5" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
+    <row r="11" ht="172.5" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -5118,238 +5310,46 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[190.0, 257.0, 286.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 14}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[190.0, 257.0, 286.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>[[190.0, 257.0, 286.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>2068722755382386</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0021.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="172.5" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 12}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>2299605336486020</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0003.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="172.5" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 14}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2497391323432836</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0017.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="172.5" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 14}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K11" t="n">
-        <v>3380173888818303</v>
+        <v>4086985684061871</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0005.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0006.png</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0005.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0006.json</t>
         </is>
       </c>
     </row>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 1}</t>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5404,16 +5404,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>3826916508657120</v>
+        <v>4593037547814288</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0001.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0018.png</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0001.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0018.json</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,455 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What integer equivalent resistance does this resistor network have between A and B?
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>4629909462371148</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0012.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="172.5" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 16}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>4790006567861593</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0020.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="172.5" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 11}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>5530123808821540</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0003.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="172.5" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 13}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>5951347384937450</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0013.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="172.5" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. What integer equivalent resistance does this resistor network have between A and B?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. What integer equivalent resistance does this resistor network have between A and B?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>6252074390446951</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0019.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="172.5" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>7249826315051981</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0000.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="172.5" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>7294685276096767</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0024.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="172.5" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -5438,63 +5886,191 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What integer equivalent resistance does this resistor network have between A and B?
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 12}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>4947651378094025</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0006.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0006.json</t>
+      <c r="K20" t="n">
+        <v>7666544514805004</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0007.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0007.json</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="172.5" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
+    <row r="21" ht="172.5" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>8139340741243868</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0015.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="172.5" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>8182743354568348</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0004.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="172.5" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -5502,63 +6078,63 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>5027780694797899</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0015.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0015.json</t>
+      <c r="K23" t="n">
+        <v>8311850786655402</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0008.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0008.json</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="172.5" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
+    <row r="24" ht="172.5" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. What integer equivalent resistance does this resistor network have between A and B?
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. What integer equivalent resistance does this resistor network have between A and B?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -5566,63 +6142,63 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. What integer equivalent resistance does this resistor network have between A and B?
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. What integer equivalent resistance does this resistor network have between A and B?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K15" t="n">
-        <v>5138198624586159</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0009.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0009.json</t>
+      <c r="K24" t="n">
+        <v>8377743133110179</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0011.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0011.json</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="172.5" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
+    <row r="25" ht="172.5" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Work from the labeled resistor boxes between terminals A and B. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Work from the labeled resistor boxes between terminals A and B. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -5630,447 +6206,63 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Work from the labeled resistor boxes between terminals A and B. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>5186789823409140</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0016.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="172.5" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Work from the labeled resistor boxes between terminals A and B. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 17}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>5944729093912585</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0022.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0022.json</t>
+      <c r="K25" t="n">
+        <v>8500079246638706</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0010.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0010.json</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="172.5" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
+    <row r="26" ht="172.5" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Determine the requested equivalent resistance from the diagram. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Determine the requested equivalent resistance from the diagram. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>6148348830281278</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0024.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="172.5" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 11}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>7249862871102077</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0008.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0008.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="172.5" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 17}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>7513188673007291</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0018.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0018.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="172.5" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>7790233719936158</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0019.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="172.5" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>7830445062449040</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0012.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0012.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="172.5" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What integer equivalent resistance does this resistor network have between A and B?
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -6078,238 +6270,46 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What integer equivalent resistance does this resistor network have between A and B?
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 18}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K23" t="n">
-        <v>7935148462875896</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0014.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="172.5" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Determine the requested equivalent resistance from the diagram. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Determine the requested equivalent resistance from the diagram. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>7985343017561541</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0002.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="172.5" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 18}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8514324742857824</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0000.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0000.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="172.5" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 13}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>8812400365677262</v>
+        <v>8923980951528888</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0007.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0009.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0007.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0009.json</t>
         </is>
       </c>
     </row>

--- a/task-reviews/physics/task_physics_circuits_equivalent_resistance/task_physics_circuits_equivalent_resistance.xlsx
+++ b/task-reviews/physics/task_physics_circuits_equivalent_resistance/task_physics_circuits_equivalent_resistance.xlsx
@@ -1184,206 +1184,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3657600" cy="2190750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3657600" cy="2190750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3657600" cy="2190750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="45" name="Image 45" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3657600" cy="2190750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="46" name="Image 46" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3657600" cy="2190750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="47" name="Image 47" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3657600" cy="2190750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="48" name="Image 48" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3657600" cy="2190750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="49" name="Image 49" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3657600" cy="2190750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="50" name="Image 50" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -2629,6 +2429,206 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2190750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2931,7 +2931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3029,7 +3029,391 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>39185639326284</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0015.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="172.5" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Answer using only the resistor values shown in the network. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Answer using only the resistor values shown in the network. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>205676244115051</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0003.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="172.5" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>418977592921915</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0004.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="172.5" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>437924746508586</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0005.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="172.5" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>945423047749785</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0006.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="172.5" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Determine the requested equivalent resistance from the diagram. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Determine the requested equivalent resistance from the diagram. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1351017546901334</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0020.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="172.5" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3037,63 +3421,127 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1474459048523441</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0021.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="172.5" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>[[85.0, 257.0, 181.0, 303.0]]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>278772381202056</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0007.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0007.json</t>
+      <c r="K9" t="n">
+        <v>1680700451011549</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0008.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0008.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="172.5" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="10" ht="172.5" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>missing_resistor_value</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3101,63 +3549,127 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1926147751723478</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0017.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="172.5" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>[[176.0, 353.0, 272.0, 399.0]]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>418977592921915</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0005.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0005.json</t>
+      <c r="K11" t="n">
+        <v>4629909462371148</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0013.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0013.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="172.5" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="12" ht="172.5" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>missing_resistor_value</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3165,63 +3677,63 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>712844117119872</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0012.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0012.json</t>
+      <c r="K12" t="n">
+        <v>5530123808821540</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0003.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0003.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="172.5" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="13" ht="172.5" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>missing_resistor_value</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Work from the labeled resistor boxes between terminals A and B. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3229,127 +3741,127 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Work from the labeled resistor boxes between terminals A and B. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>5927185308339051</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0024.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="172.5" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 7}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 11}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>[[176.0, 353.0, 272.0, 399.0]]</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>945423047749785</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0006.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0006.json</t>
+      <c r="K14" t="n">
+        <v>5951347384937450</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0013.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0013.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="172.5" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="15" ht="172.5" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>missing_resistor_value</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Answer using only the resistor values shown in the network. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Answer using only the resistor values shown in the network. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>985168828526994</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0004.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="172.5" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3357,127 +3869,63 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1351017546901334</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0020.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="172.5" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>1680700451011549</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0009.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0009.json</t>
+      <c r="K15" t="n">
+        <v>6252074390446951</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0019.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0019.json</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="172.5" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
+    <row r="16" ht="172.5" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>missing_resistor_value</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
 Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
@@ -3485,494 +3933,46 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>2909727922937639</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0015.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="172.5" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>3584273931974755</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0023.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="172.5" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Determine the requested equivalent resistance from the diagram. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Determine the requested equivalent resistance from the diagram. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>3779473663499662</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0010.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="172.5" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>3906255867824926</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0019.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="172.5" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Use the resistor values shown in the boxes to answer the question. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 11}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>4212431905210786</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0008.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0008.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="172.5" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>4614071103821109</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0017.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="172.5" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>5189991571579559</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0002.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="172.5" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Answer using only the resistor values shown in the network. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Answer using only the resistor values shown in the network. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K16" t="n">
-        <v>5192253131022505</v>
+        <v>6717988806220528</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0000.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0024.png</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0000.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0024.json</t>
         </is>
       </c>
     </row>
@@ -3988,262 +3988,6 @@
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. The two shown resistor networks are equal in total resistance between A and B. What integer resistor value belongs in the red `?` box on the left?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>6662188879944179</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0021.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="172.5" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 12}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>6717988806220528</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0024.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="172.5" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>6753696303575526</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0016.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="172.5" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 10}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>6994361047359585</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0011.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="172.5" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
@@ -4253,7 +3997,7 @@
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
 Return a valid JSON object with key "answer".
@@ -4262,14 +4006,270 @@
 {"answer":8}</t>
         </is>
       </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>7001841890215397</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0012.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="172.5" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>8139340741243868</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0015.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="172.5" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Use the resistor values shown in the boxes to answer the question. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>8311850786655402</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0009.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="172.5" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Determine the requested equivalent resistance from the diagram. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Determine the requested equivalent resistance from the diagram. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>8405728320064799</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0014.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="172.5" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>missing_resistor_value</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"evidence":[[2,3,4,5]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>The image shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Work from the labeled resistor boxes between terminals A and B. Both circuits shown have the same total resistance between terminals A and B. What integer value must the red `?` resistor in the left network have?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 3}</t>
+          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 9}</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
+          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -4283,16 +4283,16 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>7001841890215397</v>
+        <v>8500079246638706</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0013.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0011.png</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0013.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0011.json</t>
         </is>
       </c>
     </row>
@@ -4309,17 +4309,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
+Evidence format: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
+Answer requirement: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
 {"evidence":[[2,3,4,5]],"answer":8}</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Look at the resistor-network diagram in the image. It shows two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
+          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Read the resistor values and determine the requested equivalent resistance. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
 Example JSON:
@@ -4328,12 +4328,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[85.0, 257.0, 181.0, 303.0]], "answer": 8}</t>
+          <t>{"evidence": [[176.0, 273.0, 272.0, 319.0]], "answer": 3}</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>[[85.0, 257.0, 181.0, 303.0]]</t>
+          <t>[[176.0, 273.0, 272.0, 319.0]]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -4347,272 +4347,16 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>7098362396424255</v>
+        <v>8923980951528888</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0003.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0009.png</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="172.5" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Work from the labeled resistor boxes between terminals A and B. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Work from the labeled resistor boxes between terminals A and B. The left and right circuits have the same total equivalent resistance between terminals A and B. What integer value should replace the red `?` resistor in the left circuit?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 193.0, 272.0, 239.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 193.0, 272.0, 239.0]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>7433576612134137</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0001.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0001.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="172.5" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer field: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Read the resistor values and determine the requested equivalent resistance. One resistor in the left circuit is marked with a red `?`. If both circuits have equal total resistance between A and B, what value must replace it? Answer with an integer.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>7643448629001720</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0018.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0018.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="172.5" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor inside a parallel branch. Determine the requested equivalent resistance from the diagram. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 10}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8405728320064799</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0014.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="172.5" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>missing_resistor_value</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array with the single bounding box [x1, y1, x2, y2] of the red `?` resistor in the left circuit.
-Answer format: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"evidence":[[2,3,4,5]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: two side-by-side resistor networks between labeled terminals A and B that have the same total resistance, where the left circuit has one red `?` resistor in the series part of the network. Answer using only the resistor values shown in the network. Use the fact that the left and right circuits have the same equivalent resistance between A and B. What value should the red `?` resistor on the left be? Answer with an integer.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the integer resistor value that should replace the red `?` resistor.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[176.0, 353.0, 272.0, 399.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[176.0, 353.0, 272.0, 399.0]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>8414218812010040</v>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0022.png</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0022.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0009.json</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4726,7 +4470,199 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>278772381202056</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0006.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="172.5" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 16}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>712844117119872</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0012.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="172.5" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 14}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>985168828526994</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0004.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="172.5" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -4734,215 +4670,23 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>39185639326284</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0014.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="172.5" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What integer equivalent resistance does this resistor network have between A and B?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What integer equivalent resistance does this resistor network have between A and B?
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[654.0, 257.0, 750.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 7}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>[[654.0, 257.0, 750.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>205676244115051</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0002.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="172.5" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>437924746508586</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0005.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0005.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="172.5" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B with three or four parallel labeled resistor branches. Determine the requested equivalent resistance from the diagram. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B with three or four parallel labeled resistor branches. Determine the requested equivalent resistance from the diagram. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 7}</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4960,12 +4704,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0017.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0017.png</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0017.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0017.json</t>
         </is>
       </c>
     </row>
@@ -4981,134 +4725,6 @@
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 10}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1474459048523441</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0021.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="172.5" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1926147751723478</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0016.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="172.5" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
@@ -5118,7 +4734,7 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
@@ -5127,52 +4743,116 @@
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K6" t="n">
         <v>2093720560009143</v>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0023.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0023.json</t>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0023.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0023.json</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="172.5" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
+    <row r="7" ht="172.5" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2909727922937639</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0014.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="172.5" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
@@ -5182,7 +4862,7 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
@@ -5191,6 +4871,70 @@
 {"answer":8}</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 17}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>3309929876814048</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0023.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="172.5" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 16}</t>
@@ -5212,16 +4956,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3309929876814048</v>
+        <v>3584273931974755</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0022.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0022.png</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0022.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0022.json</t>
         </is>
       </c>
     </row>
@@ -5257,12 +5001,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[654.0, 257.0, 750.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 10}</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>[[654.0, 257.0, 750.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -5280,12 +5024,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0001.png</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0001.png</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0001.json</t>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0001.json</t>
         </is>
       </c>
     </row>
@@ -5301,6 +5045,134 @@
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[190.0, 257.0, 286.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[190.0, 257.0, 286.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3779473663499662</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0010.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="172.5" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>3906255867824926</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0018.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="172.5" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
@@ -5310,7 +5182,7 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
@@ -5319,54 +5191,118 @@
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[190.0, 257.0, 286.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 12}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[190.0, 257.0, 286.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>[[190.0, 257.0, 286.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K13" t="n">
         <v>4086985684061871</v>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0006.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0006.json</t>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0007.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0007.json</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="172.5" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
+    <row r="14" ht="172.5" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>4212431905210786</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0008.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="172.5" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -5374,125 +5310,125 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K15" t="n">
         <v>4593037547814288</v>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0018.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0018.json</t>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0019.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0019.json</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="172.5" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
+    <row r="16" ht="172.5" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 13}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>4629909462371148</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0012.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0012.json</t>
+      <c r="K16" t="n">
+        <v>4614071103821109</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0016.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0016.json</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="172.5" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
+    <row r="17" ht="172.5" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
@@ -5502,7 +5438,7 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
@@ -5511,54 +5447,118 @@
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 16}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 11}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K17" t="n">
         <v>4790006567861593</v>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0020.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0020.json</t>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0021.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0021.json</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="172.5" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
+    <row r="18" ht="172.5" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>5189991571579559</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0002.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="172.5" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What integer equivalent resistance does this resistor network have between A and B?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -5566,63 +5566,63 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What integer equivalent resistance does this resistor network have between A and B?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 11}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K15" t="n">
-        <v>5530123808821540</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0003.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0003.json</t>
+      <c r="K19" t="n">
+        <v>5192253131022505</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0000.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0000.json</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="172.5" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
+    <row r="20" ht="172.5" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -5630,63 +5630,191 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 13}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 14}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>5951347384937450</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0013.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0013.json</t>
+      <c r="K20" t="n">
+        <v>6662188879944179</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0020.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0020.json</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="172.5" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
+    <row r="21" ht="172.5" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. What integer equivalent resistance does this resistor network have between A and B?
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 7}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6753696303575526</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0016.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="172.5" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Determine the requested equivalent resistance from the diagram. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 11}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>6994361047359585</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0010.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="172.5" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -5694,61 +5822,61 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. What integer equivalent resistance does this resistor network have between A and B?
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 18}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>6252074390446951</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0019.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0019.json</t>
+      <c r="K23" t="n">
+        <v>7098362396424255</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0002.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0002.json</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="172.5" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
+    <row r="24" ht="172.5" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
@@ -5758,7 +5886,7 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>You are given an image with one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
@@ -5767,54 +5895,374 @@
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 13}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K18" t="n">
+      <c r="K24" t="n">
         <v>7249826315051981</v>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0000.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0000.json</t>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0001.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0001.json</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="172.5" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
+    <row r="25" ht="172.5" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>task_physics_circuits_equivalent_resistance</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>total_resistance</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]], "answer": 16}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>7433576612134137</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0000.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="172.5" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>7643448629001720</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0018.png</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="172.5" customHeight="1">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 17}</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>7666544514805004</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0007.png</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="172.5" customHeight="1">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>The image shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[654.0, 257.0, 750.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>[[654.0, 257.0, 750.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>8182743354568348</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0005.png</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="172.5" customHeight="1">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. What integer equivalent resistance does this resistor network have between A and B?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Use the resistor values shown in the boxes to answer the question. What integer equivalent resistance does this resistor network have between A and B?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>[[593.0, 257.0, 689.0, 303.0], [715.0, 257.0, 811.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>8377743133110179</v>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/missing_resistor_value/0011.png</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/missing_resistor_value/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="172.5" customHeight="1">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>task_physics_circuits_equivalent_resistance</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>total_resistance</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
 Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
@@ -5822,494 +6270,46 @@
 {"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Use the circuit diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>7294685276096767</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0024.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="172.5" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B with three or four parallel labeled resistor branches. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>7666544514805004</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0007.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="172.5" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Work from the labeled resistor boxes between terminals A and B. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>8139340741243868</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0015.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="172.5" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 247.0, 518.0, 293.0], [422.0, 327.0, 518.0, 373.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>8182743354568348</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0004.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="172.5" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. Read the circuit between terminals A and B. What is its total equivalent resistance? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>8311850786655402</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0008.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0008.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="172.5" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. What integer equivalent resistance does this resistor network have between A and B?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Look at the resistor-network diagram in the image. It shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Use the resistor values shown in the boxes to answer the question. What integer equivalent resistance does this resistor network have between A and B?
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Work from the resistor-network diagram shown in the image: one resistor network between terminals A and B that combines a short series chain with a parallel resistor bank. Answer using only the resistor values shown in the network. Using the resistor values shown, what equivalent resistance is seen between terminals A and B? Answer with an integer number of ohms.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 17}</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>[[129.0, 257.0, 225.0, 303.0], [251.0, 257.0, 347.0, 303.0], [422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K24" t="n">
-        <v>8377743133110179</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0011.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="172.5" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Work from the labeled resistor boxes between terminals A and B. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer field: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>The image shows one resistor network between terminals A and B with three or four parallel labeled resistor branches. Work from the labeled resistor boxes between terminals A and B. What is the total equivalent resistance between terminals A and B? Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8500079246638706</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0010.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="172.5" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_physics_circuits_equivalent_resistance</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>total_resistance</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array of bounding boxes [x1, y1, x2, y2] for all resistor boxes that belong to the network between terminals A and B.
-Answer requirement: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"evidence":[[2,3,4,5],[3,4,5,6],[4,5,6,7]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with one resistor network between terminals A and B with three or four parallel labeled resistor branches. Read the resistor values and determine the requested equivalent resistance. Determine the network's total resistance between A and B. Answer with an integer number of ohms.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the total equivalent resistance between terminals A and B as an integer number of ohms.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[422.0, 167.0, 518.0, 213.0], [422.0, 287.0, 518.0, 333.0], [422.0, 407.0, 518.0, 453.0]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>8923980951528888</v>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0009.png</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0009.json</t>
+      <c r="K30" t="n">
+        <v>8414218812010040</v>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/images/total_resistance/0022.png</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>physics/task_physics_circuits_equivalent_resistance/data/total_resistance/0022.json</t>
         </is>
       </c>
     </row>
